--- a/activity/M01A00/M01A00_CasoEstudio.xlsx
+++ b/activity/M01A00/M01A00_CasoEstudio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A00\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B48F703-F1EE-4F22-AC6D-918DBAB5A81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEF3681-2AA6-4DDE-B2D3-3C683719356D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
   <si>
     <t>Tipo</t>
   </si>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>Autocalificación alumno</t>
-  </si>
-  <si>
-    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A00/Readme.md</t>
   </si>
   <si>
     <t>Resumen general del proyecto</t>
@@ -232,12 +229,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="10"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
@@ -261,6 +252,12 @@
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -276,7 +273,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -417,15 +414,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -561,7 +549,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -635,7 +623,7 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -647,13 +635,13 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
@@ -665,35 +653,59 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -701,38 +713,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2097,40 +2082,40 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
       <c r="F1" s="31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="B2" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
     </row>
     <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
@@ -2220,7 +2205,7 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B10" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="25">
         <v>5</v>
@@ -2237,7 +2222,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="25">
         <v>5</v>
@@ -2254,7 +2239,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" s="25">
         <v>5</v>
@@ -2271,7 +2256,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="25">
         <v>5</v>
@@ -2288,7 +2273,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="25">
         <v>5</v>
@@ -2305,7 +2290,7 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="25">
         <v>5</v>
@@ -2322,7 +2307,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="25">
         <v>5</v>
@@ -2339,7 +2324,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="25">
         <v>5</v>
@@ -2356,7 +2341,7 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="29">
         <v>5</v>
@@ -2372,20 +2357,21 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
+      <c r="B19" s="56" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
+        <v>Ir a actividad M01A00 en GitHub.</v>
+      </c>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="30"/>
@@ -2395,17 +2381,15 @@
       <c r="F21" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
-    <mergeCell ref="B19:F20"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B19" r:id="rId1" xr:uid="{B1817C3D-E587-407A-8D66-AAA0AD88E73B}"/>
-  </hyperlinks>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2475,76 +2459,76 @@
       <c r="B2" s="35"/>
       <c r="C2" s="36"/>
       <c r="D2" s="37"/>
-      <c r="E2" s="47" t="str">
+      <c r="E2" s="46" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="F2" s="48"/>
-      <c r="G2" s="47" t="str">
+      <c r="F2" s="47"/>
+      <c r="G2" s="46" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="H2" s="48"/>
-      <c r="I2" s="47" t="str">
+      <c r="H2" s="47"/>
+      <c r="I2" s="46" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="48"/>
-      <c r="K2" s="51" t="str">
+      <c r="J2" s="47"/>
+      <c r="K2" s="49" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="L2" s="48"/>
-      <c r="M2" s="47" t="str">
+      <c r="L2" s="47"/>
+      <c r="M2" s="46" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="N2" s="48"/>
-      <c r="O2" s="47" t="str">
+      <c r="N2" s="47"/>
+      <c r="O2" s="46" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="47" t="str">
+      <c r="P2" s="47"/>
+      <c r="Q2" s="46" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="R2" s="48"/>
-      <c r="S2" s="47" t="str">
+      <c r="R2" s="47"/>
+      <c r="S2" s="46" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="T2" s="48"/>
-      <c r="U2" s="47" t="str">
+      <c r="T2" s="47"/>
+      <c r="U2" s="46" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="V2" s="48"/>
-      <c r="W2" s="47" t="str">
+      <c r="V2" s="47"/>
+      <c r="W2" s="46" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="47" t="str">
+      <c r="X2" s="47"/>
+      <c r="Y2" s="46" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="Z2" s="48"/>
-      <c r="AA2" s="47" t="str">
+      <c r="Z2" s="47"/>
+      <c r="AA2" s="46" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AB2" s="48"/>
-      <c r="AC2" s="47" t="str">
+      <c r="AB2" s="47"/>
+      <c r="AC2" s="46" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AD2" s="48"/>
-      <c r="AE2" s="47" t="str">
+      <c r="AD2" s="47"/>
+      <c r="AE2" s="46" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AF2" s="48"/>
+      <c r="AF2" s="47"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="B3" s="4" t="s">
@@ -2642,11 +2626,11 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="50" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="17">
         <v>1</v>
@@ -2709,9 +2693,9 @@
       <c r="AF4" s="6"/>
     </row>
     <row r="5" spans="1:32" ht="33" x14ac:dyDescent="0.45">
-      <c r="B5" s="56"/>
+      <c r="B5" s="51"/>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="17">
         <v>1</v>
@@ -2746,7 +2730,7 @@
       <c r="AF5" s="6"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B6" s="56"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
@@ -2783,9 +2767,9 @@
       <c r="AF6" s="6"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B7" s="56"/>
+      <c r="B7" s="51"/>
       <c r="C7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="17">
         <v>1</v>
@@ -2820,9 +2804,9 @@
       <c r="AF7" s="6"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B8" s="56"/>
+      <c r="B8" s="51"/>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="17">
         <v>1</v>
@@ -2857,7 +2841,7 @@
       <c r="AF8" s="6"/>
     </row>
     <row r="9" spans="1:32" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="56"/>
+      <c r="B9" s="51"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
@@ -2894,9 +2878,9 @@
       <c r="AF9" s="6"/>
     </row>
     <row r="10" spans="1:32" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="56"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="17">
         <v>1</v>
@@ -2931,41 +2915,41 @@
       <c r="AF10" s="6"/>
     </row>
     <row r="11" spans="1:32" ht="132" x14ac:dyDescent="0.45">
-      <c r="B11" s="57"/>
-      <c r="C11" s="52" t="s">
-        <v>36</v>
+      <c r="B11" s="52"/>
+      <c r="C11" s="41" t="s">
+        <v>35</v>
       </c>
       <c r="D11" s="17">
         <v>1</v>
       </c>
-      <c r="E11" s="53"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="53"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="53"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="53"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="53"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="53"/>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="53"/>
-      <c r="Z11" s="54"/>
-      <c r="AA11" s="53"/>
-      <c r="AB11" s="54"/>
-      <c r="AC11" s="53"/>
-      <c r="AD11" s="54"/>
-      <c r="AE11" s="53"/>
-      <c r="AF11" s="54"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="42"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="42"/>
+      <c r="X11" s="43"/>
+      <c r="Y11" s="42"/>
+      <c r="Z11" s="43"/>
+      <c r="AA11" s="42"/>
+      <c r="AB11" s="43"/>
+      <c r="AC11" s="42"/>
+      <c r="AD11" s="43"/>
+      <c r="AE11" s="42"/>
+      <c r="AF11" s="43"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.45">
       <c r="B12" s="12"/>
@@ -3001,91 +2985,91 @@
       <c r="AF12" s="8"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B13" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="50">
+      <c r="B13" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="48">
         <f>AVERAGE(E4:E12)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50">
+      <c r="F13" s="48"/>
+      <c r="G13" s="48">
         <f>AVERAGE(G4:G12)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50">
+      <c r="H13" s="48"/>
+      <c r="I13" s="48">
         <f>AVERAGE(I4:I12)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50">
+      <c r="J13" s="48"/>
+      <c r="K13" s="48">
         <f>AVERAGE(K4:K12)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50">
+      <c r="L13" s="48"/>
+      <c r="M13" s="48">
         <f>AVERAGE(M4:M12)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50">
+      <c r="N13" s="48"/>
+      <c r="O13" s="48">
         <f>AVERAGE(O4:O12)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50">
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48">
         <f>AVERAGE(Q4:Q12)</f>
         <v>0</v>
       </c>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50">
+      <c r="R13" s="48"/>
+      <c r="S13" s="48">
         <f>AVERAGE(S4:S12)</f>
         <v>0</v>
       </c>
-      <c r="T13" s="50"/>
-      <c r="U13" s="50">
+      <c r="T13" s="48"/>
+      <c r="U13" s="48">
         <f>AVERAGE(U4:U12)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="50"/>
-      <c r="W13" s="50">
+      <c r="V13" s="48"/>
+      <c r="W13" s="48">
         <f>AVERAGE(W4:W12)</f>
         <v>0</v>
       </c>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="50">
+      <c r="X13" s="48"/>
+      <c r="Y13" s="48">
         <f>AVERAGE(Y4:Y12)</f>
         <v>0</v>
       </c>
-      <c r="Z13" s="50"/>
-      <c r="AA13" s="50">
+      <c r="Z13" s="48"/>
+      <c r="AA13" s="48">
         <f>AVERAGE(AA4:AA12)</f>
         <v>0</v>
       </c>
-      <c r="AB13" s="50"/>
-      <c r="AC13" s="50">
+      <c r="AB13" s="48"/>
+      <c r="AC13" s="48">
         <f>AVERAGE(AC4:AC12)</f>
         <v>0</v>
       </c>
-      <c r="AD13" s="50"/>
-      <c r="AE13" s="50">
+      <c r="AD13" s="48"/>
+      <c r="AE13" s="48">
         <f>AVERAGE(AE4:AE12)</f>
         <v>0</v>
       </c>
-      <c r="AF13" s="50"/>
+      <c r="AF13" s="48"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B14" s="45"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
     </row>
     <row r="23" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C23" s="2"/>
@@ -3137,20 +3121,7 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AC13:AD13"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="B4:B11"/>
     <mergeCell ref="B14:D15"/>
     <mergeCell ref="AE2:AF2"/>
@@ -3167,7 +3138,20 @@
     <mergeCell ref="W13:X13"/>
     <mergeCell ref="Y13:Z13"/>
     <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AE13:AF13"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AC13:AD13"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/activity/M01A00/M01A00_CasoEstudio.xlsx
+++ b/activity/M01A00/M01A00_CasoEstudio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A00\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEF3681-2AA6-4DDE-B2D3-3C683719356D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7AF916-5DEC-4772-BC9A-DF7615452F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -686,38 +686,38 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -809,9 +809,9 @@
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
           <c:x val="0.13451837270341208"/>
-          <c:y val="0.14726960784313725"/>
+          <c:y val="0.16294876543209877"/>
           <c:w val="0.83492607174103239"/>
-          <c:h val="0.58865647220019413"/>
+          <c:h val="0.5729774691358025"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -835,7 +835,7 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="bg1">
-                <a:lumMod val="50000"/>
+                <a:lumMod val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -844,6 +844,60 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Calificacion!$B$5:$B$9</c:f>
@@ -2357,21 +2411,21 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="56" t="str">
+      <c r="B19" s="46" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A00 en GitHub.</v>
       </c>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="30"/>
@@ -2459,76 +2513,76 @@
       <c r="B2" s="35"/>
       <c r="C2" s="36"/>
       <c r="D2" s="37"/>
-      <c r="E2" s="46" t="str">
+      <c r="E2" s="53" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="F2" s="47"/>
-      <c r="G2" s="46" t="str">
+      <c r="F2" s="54"/>
+      <c r="G2" s="53" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="H2" s="47"/>
-      <c r="I2" s="46" t="str">
+      <c r="H2" s="54"/>
+      <c r="I2" s="53" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="47"/>
-      <c r="K2" s="49" t="str">
+      <c r="J2" s="54"/>
+      <c r="K2" s="56" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="L2" s="47"/>
-      <c r="M2" s="46" t="str">
+      <c r="L2" s="54"/>
+      <c r="M2" s="53" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="46" t="str">
+      <c r="N2" s="54"/>
+      <c r="O2" s="53" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="46" t="str">
+      <c r="P2" s="54"/>
+      <c r="Q2" s="53" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="R2" s="47"/>
-      <c r="S2" s="46" t="str">
+      <c r="R2" s="54"/>
+      <c r="S2" s="53" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="T2" s="47"/>
-      <c r="U2" s="46" t="str">
+      <c r="T2" s="54"/>
+      <c r="U2" s="53" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="V2" s="47"/>
-      <c r="W2" s="46" t="str">
+      <c r="V2" s="54"/>
+      <c r="W2" s="53" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="X2" s="47"/>
-      <c r="Y2" s="46" t="str">
+      <c r="X2" s="54"/>
+      <c r="Y2" s="53" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="Z2" s="47"/>
-      <c r="AA2" s="46" t="str">
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="53" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AB2" s="47"/>
-      <c r="AC2" s="46" t="str">
+      <c r="AB2" s="54"/>
+      <c r="AC2" s="53" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AD2" s="47"/>
-      <c r="AE2" s="46" t="str">
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="53" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AF2" s="47"/>
+      <c r="AF2" s="54"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="B3" s="4" t="s">
@@ -2626,7 +2680,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="48" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -2693,7 +2747,7 @@
       <c r="AF4" s="6"/>
     </row>
     <row r="5" spans="1:32" ht="33" x14ac:dyDescent="0.45">
-      <c r="B5" s="51"/>
+      <c r="B5" s="49"/>
       <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
@@ -2730,7 +2784,7 @@
       <c r="AF5" s="6"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B6" s="51"/>
+      <c r="B6" s="49"/>
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
@@ -2767,7 +2821,7 @@
       <c r="AF6" s="6"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B7" s="51"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
@@ -2804,7 +2858,7 @@
       <c r="AF7" s="6"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B8" s="51"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
@@ -2841,7 +2895,7 @@
       <c r="AF8" s="6"/>
     </row>
     <row r="9" spans="1:32" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="51"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
@@ -2878,7 +2932,7 @@
       <c r="AF9" s="6"/>
     </row>
     <row r="10" spans="1:32" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="51"/>
+      <c r="B10" s="49"/>
       <c r="C10" s="3" t="s">
         <v>19</v>
       </c>
@@ -2915,7 +2969,7 @@
       <c r="AF10" s="6"/>
     </row>
     <row r="11" spans="1:32" ht="132" x14ac:dyDescent="0.45">
-      <c r="B11" s="52"/>
+      <c r="B11" s="50"/>
       <c r="C11" s="41" t="s">
         <v>35</v>
       </c>
@@ -2923,7 +2977,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="42"/>
-      <c r="F11" s="43"/>
+      <c r="F11" s="6"/>
       <c r="G11" s="42"/>
       <c r="H11" s="43"/>
       <c r="I11" s="42"/>
@@ -2990,86 +3044,86 @@
       </c>
       <c r="C13" s="55"/>
       <c r="D13" s="55"/>
-      <c r="E13" s="48">
+      <c r="E13" s="47">
         <f>AVERAGE(E4:E12)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48">
+      <c r="F13" s="47"/>
+      <c r="G13" s="47">
         <f>AVERAGE(G4:G12)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48">
+      <c r="H13" s="47"/>
+      <c r="I13" s="47">
         <f>AVERAGE(I4:I12)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48">
+      <c r="J13" s="47"/>
+      <c r="K13" s="47">
         <f>AVERAGE(K4:K12)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48">
+      <c r="L13" s="47"/>
+      <c r="M13" s="47">
         <f>AVERAGE(M4:M12)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="48"/>
-      <c r="O13" s="48">
+      <c r="N13" s="47"/>
+      <c r="O13" s="47">
         <f>AVERAGE(O4:O12)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="48">
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47">
         <f>AVERAGE(Q4:Q12)</f>
         <v>0</v>
       </c>
-      <c r="R13" s="48"/>
-      <c r="S13" s="48">
+      <c r="R13" s="47"/>
+      <c r="S13" s="47">
         <f>AVERAGE(S4:S12)</f>
         <v>0</v>
       </c>
-      <c r="T13" s="48"/>
-      <c r="U13" s="48">
+      <c r="T13" s="47"/>
+      <c r="U13" s="47">
         <f>AVERAGE(U4:U12)</f>
         <v>0</v>
       </c>
-      <c r="V13" s="48"/>
-      <c r="W13" s="48">
+      <c r="V13" s="47"/>
+      <c r="W13" s="47">
         <f>AVERAGE(W4:W12)</f>
         <v>0</v>
       </c>
-      <c r="X13" s="48"/>
-      <c r="Y13" s="48">
+      <c r="X13" s="47"/>
+      <c r="Y13" s="47">
         <f>AVERAGE(Y4:Y12)</f>
         <v>0</v>
       </c>
-      <c r="Z13" s="48"/>
-      <c r="AA13" s="48">
+      <c r="Z13" s="47"/>
+      <c r="AA13" s="47">
         <f>AVERAGE(AA4:AA12)</f>
         <v>0</v>
       </c>
-      <c r="AB13" s="48"/>
-      <c r="AC13" s="48">
+      <c r="AB13" s="47"/>
+      <c r="AC13" s="47">
         <f>AVERAGE(AC4:AC12)</f>
         <v>0</v>
       </c>
-      <c r="AD13" s="48"/>
-      <c r="AE13" s="48">
+      <c r="AD13" s="47"/>
+      <c r="AE13" s="47">
         <f>AVERAGE(AE4:AE12)</f>
         <v>0</v>
       </c>
-      <c r="AF13" s="48"/>
+      <c r="AF13" s="47"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B14" s="53"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
     </row>
     <row r="23" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C23" s="2"/>
@@ -3121,6 +3175,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AC13:AD13"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AA2:AB2"/>
     <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="B4:B11"/>
     <mergeCell ref="B14:D15"/>
@@ -3137,21 +3206,6 @@
     <mergeCell ref="U13:V13"/>
     <mergeCell ref="W13:X13"/>
     <mergeCell ref="Y13:Z13"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AC13:AD13"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/activity/M01A00/M01A00_CasoEstudio.xlsx
+++ b/activity/M01A00/M01A00_CasoEstudio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29205"/>
   <workbookPr updateLinks="never" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A00\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7AF916-5DEC-4772-BC9A-DF7615452F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8AB52E-4A44-4282-BC85-784E1387032C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="13" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Calificacion!$B$2:$F$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">RealineamientoReportado!$B$2:$D$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">RealineamientoReportado!$B$2:$D$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">RealineamientoReportado!$2:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
   <si>
     <t>Tipo</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>Informe técnico mostrando las actividades desarrolladas en el orden presentado en esta actividad, junto con los análisis y recomendaciones realizadas, convierta a Adobe Acrobat (.pdf) y guarde en la carpeta /report del repositorio de datos del proyecto.</t>
+  </si>
+  <si>
+    <t>Parámetros ambientales</t>
   </si>
 </sst>
 </file>
@@ -689,6 +692,15 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -707,17 +719,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2180,7 +2183,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="24">
-        <f>RealineamientoReportado!E13</f>
+        <f>RealineamientoReportado!E14</f>
         <v>0</v>
       </c>
       <c r="E5" s="25"/>
@@ -2197,7 +2200,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="24">
-        <f>RealineamientoReportado!G13</f>
+        <f>RealineamientoReportado!G14</f>
         <v>0</v>
       </c>
       <c r="E6" s="25"/>
@@ -2214,7 +2217,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="24">
-        <f>RealineamientoReportado!I13</f>
+        <f>RealineamientoReportado!I14</f>
         <v>0</v>
       </c>
       <c r="E7" s="25"/>
@@ -2231,7 +2234,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="24">
-        <f>RealineamientoReportado!K13</f>
+        <f>RealineamientoReportado!K14</f>
         <v>0</v>
       </c>
       <c r="E8" s="25"/>
@@ -2248,7 +2251,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="24">
-        <f>RealineamientoReportado!M13</f>
+        <f>RealineamientoReportado!M14</f>
         <v>0</v>
       </c>
       <c r="E9" s="25"/>
@@ -2265,7 +2268,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="24">
-        <f>RealineamientoReportado!O13</f>
+        <f>RealineamientoReportado!O14</f>
         <v>0</v>
       </c>
       <c r="E10" s="25"/>
@@ -2282,7 +2285,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="24">
-        <f>RealineamientoReportado!Q13</f>
+        <f>RealineamientoReportado!Q14</f>
         <v>0</v>
       </c>
       <c r="E11" s="25"/>
@@ -2299,7 +2302,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="24">
-        <f>RealineamientoReportado!S13</f>
+        <f>RealineamientoReportado!S14</f>
         <v>0</v>
       </c>
       <c r="E12" s="25"/>
@@ -2316,7 +2319,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="24">
-        <f>RealineamientoReportado!U13</f>
+        <f>RealineamientoReportado!U14</f>
         <v>0</v>
       </c>
       <c r="E13" s="25"/>
@@ -2333,7 +2336,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="24">
-        <f>RealineamientoReportado!W13</f>
+        <f>RealineamientoReportado!W14</f>
         <v>0</v>
       </c>
       <c r="E14" s="25"/>
@@ -2350,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="24">
-        <f>RealineamientoReportado!Y13</f>
+        <f>RealineamientoReportado!Y14</f>
         <v>0</v>
       </c>
       <c r="E15" s="25"/>
@@ -2367,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="24">
-        <f>RealineamientoReportado!AA13</f>
+        <f>RealineamientoReportado!AA14</f>
         <v>0</v>
       </c>
       <c r="E16" s="25"/>
@@ -2384,7 +2387,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="40">
-        <f>RealineamientoReportado!AC13</f>
+        <f>RealineamientoReportado!AC14</f>
         <v>0</v>
       </c>
       <c r="E17" s="39"/>
@@ -2401,7 +2404,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="28">
-        <f>RealineamientoReportado!AE13</f>
+        <f>RealineamientoReportado!AE14</f>
         <v>0</v>
       </c>
       <c r="E18" s="29"/>
@@ -2449,7 +2452,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6131B6-D0CB-405A-ABA0-C146745C9D16}">
-  <dimension ref="A1:AF38"/>
+  <dimension ref="A1:AF39"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -2513,76 +2516,76 @@
       <c r="B2" s="35"/>
       <c r="C2" s="36"/>
       <c r="D2" s="37"/>
-      <c r="E2" s="53" t="str">
+      <c r="E2" s="47" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="F2" s="54"/>
-      <c r="G2" s="53" t="str">
+      <c r="F2" s="48"/>
+      <c r="G2" s="47" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="H2" s="54"/>
-      <c r="I2" s="53" t="str">
+      <c r="H2" s="48"/>
+      <c r="I2" s="47" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="54"/>
-      <c r="K2" s="56" t="str">
+      <c r="J2" s="48"/>
+      <c r="K2" s="49" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="L2" s="54"/>
-      <c r="M2" s="53" t="str">
+      <c r="L2" s="48"/>
+      <c r="M2" s="47" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="N2" s="54"/>
-      <c r="O2" s="53" t="str">
+      <c r="N2" s="48"/>
+      <c r="O2" s="47" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="53" t="str">
+      <c r="P2" s="48"/>
+      <c r="Q2" s="47" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="R2" s="54"/>
-      <c r="S2" s="53" t="str">
+      <c r="R2" s="48"/>
+      <c r="S2" s="47" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="T2" s="54"/>
-      <c r="U2" s="53" t="str">
+      <c r="T2" s="48"/>
+      <c r="U2" s="47" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="V2" s="54"/>
-      <c r="W2" s="53" t="str">
+      <c r="V2" s="48"/>
+      <c r="W2" s="47" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="X2" s="54"/>
-      <c r="Y2" s="53" t="str">
+      <c r="X2" s="48"/>
+      <c r="Y2" s="47" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="Z2" s="54"/>
-      <c r="AA2" s="53" t="str">
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="47" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AB2" s="54"/>
-      <c r="AC2" s="53" t="str">
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="47" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AD2" s="54"/>
-      <c r="AE2" s="53" t="str">
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="47" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AF2" s="54"/>
+      <c r="AF2" s="48"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="B3" s="4" t="s">
@@ -2680,7 +2683,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="51" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -2747,7 +2750,7 @@
       <c r="AF4" s="6"/>
     </row>
     <row r="5" spans="1:32" ht="33" x14ac:dyDescent="0.45">
-      <c r="B5" s="49"/>
+      <c r="B5" s="52"/>
       <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
@@ -2784,7 +2787,7 @@
       <c r="AF5" s="6"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B6" s="49"/>
+      <c r="B6" s="52"/>
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
@@ -2821,7 +2824,7 @@
       <c r="AF6" s="6"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B7" s="49"/>
+      <c r="B7" s="52"/>
       <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
@@ -2858,9 +2861,9 @@
       <c r="AF7" s="6"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B8" s="49"/>
+      <c r="B8" s="52"/>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D8" s="17">
         <v>1</v>
@@ -2894,10 +2897,10 @@
       <c r="AE8" s="10"/>
       <c r="AF8" s="6"/>
     </row>
-    <row r="9" spans="1:32" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="49"/>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B9" s="52"/>
       <c r="C9" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D9" s="17">
         <v>1</v>
@@ -2917,9 +2920,9 @@
       <c r="Q9" s="10"/>
       <c r="R9" s="6"/>
       <c r="S9" s="10"/>
-      <c r="T9" s="13"/>
+      <c r="T9" s="6"/>
       <c r="U9" s="10"/>
-      <c r="V9" s="13"/>
+      <c r="V9" s="6"/>
       <c r="W9" s="10"/>
       <c r="X9" s="6"/>
       <c r="Y9" s="10"/>
@@ -2932,9 +2935,9 @@
       <c r="AF9" s="6"/>
     </row>
     <row r="10" spans="1:32" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="49"/>
+      <c r="B10" s="52"/>
       <c r="C10" s="3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D10" s="17">
         <v>1</v>
@@ -2954,9 +2957,9 @@
       <c r="Q10" s="10"/>
       <c r="R10" s="6"/>
       <c r="S10" s="10"/>
-      <c r="T10" s="6"/>
+      <c r="T10" s="13"/>
       <c r="U10" s="10"/>
-      <c r="V10" s="6"/>
+      <c r="V10" s="13"/>
       <c r="W10" s="10"/>
       <c r="X10" s="6"/>
       <c r="Y10" s="10"/>
@@ -2968,165 +2971,199 @@
       <c r="AE10" s="10"/>
       <c r="AF10" s="6"/>
     </row>
-    <row r="11" spans="1:32" ht="132" x14ac:dyDescent="0.45">
-      <c r="B11" s="50"/>
-      <c r="C11" s="41" t="s">
-        <v>35</v>
+    <row r="11" spans="1:32" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="52"/>
+      <c r="C11" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D11" s="17">
         <v>1</v>
       </c>
-      <c r="E11" s="42"/>
+      <c r="E11" s="10"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="42"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="42"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="42"/>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="42"/>
-      <c r="Z11" s="43"/>
-      <c r="AA11" s="42"/>
-      <c r="AB11" s="43"/>
-      <c r="AC11" s="42"/>
-      <c r="AD11" s="43"/>
-      <c r="AE11" s="42"/>
-      <c r="AF11" s="43"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B12" s="12"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="11"/>
-      <c r="Z12" s="8"/>
-      <c r="AA12" s="11"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="8"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="10"/>
+      <c r="AF11" s="6"/>
+    </row>
+    <row r="12" spans="1:32" ht="132" x14ac:dyDescent="0.45">
+      <c r="B12" s="53"/>
+      <c r="C12" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="17">
+        <v>1</v>
+      </c>
+      <c r="E12" s="42"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="42"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="42"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="42"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="42"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="42"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="42"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="42"/>
+      <c r="AF12" s="43"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="12"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="11"/>
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="11"/>
+      <c r="AD13" s="8"/>
+      <c r="AE13" s="11"/>
+      <c r="AF13" s="8"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B14" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="47">
-        <f>AVERAGE(E4:E12)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47">
-        <f>AVERAGE(G4:G12)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47">
-        <f>AVERAGE(I4:I12)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47">
-        <f>AVERAGE(K4:K12)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47">
-        <f>AVERAGE(M4:M12)</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47">
-        <f>AVERAGE(O4:O12)</f>
-        <v>0</v>
-      </c>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47">
-        <f>AVERAGE(Q4:Q12)</f>
-        <v>0</v>
-      </c>
-      <c r="R13" s="47"/>
-      <c r="S13" s="47">
-        <f>AVERAGE(S4:S12)</f>
-        <v>0</v>
-      </c>
-      <c r="T13" s="47"/>
-      <c r="U13" s="47">
-        <f>AVERAGE(U4:U12)</f>
-        <v>0</v>
-      </c>
-      <c r="V13" s="47"/>
-      <c r="W13" s="47">
-        <f>AVERAGE(W4:W12)</f>
-        <v>0</v>
-      </c>
-      <c r="X13" s="47"/>
-      <c r="Y13" s="47">
-        <f>AVERAGE(Y4:Y12)</f>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="47"/>
-      <c r="AA13" s="47">
-        <f>AVERAGE(AA4:AA12)</f>
-        <v>0</v>
-      </c>
-      <c r="AB13" s="47"/>
-      <c r="AC13" s="47">
-        <f>AVERAGE(AC4:AC12)</f>
-        <v>0</v>
-      </c>
-      <c r="AD13" s="47"/>
-      <c r="AE13" s="47">
-        <f>AVERAGE(AE4:AE12)</f>
-        <v>0</v>
-      </c>
-      <c r="AF13" s="47"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B14" s="51"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="50">
+        <f>AVERAGE(E4:E13)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50">
+        <f>AVERAGE(G4:G13)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50">
+        <f>AVERAGE(I4:I13)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="50"/>
+      <c r="K14" s="50">
+        <f>AVERAGE(K4:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="50"/>
+      <c r="M14" s="50">
+        <f>AVERAGE(M4:M13)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50">
+        <f>AVERAGE(O4:O13)</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="50">
+        <f>AVERAGE(Q4:Q13)</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="50"/>
+      <c r="S14" s="50">
+        <f>AVERAGE(S4:S13)</f>
+        <v>0</v>
+      </c>
+      <c r="T14" s="50"/>
+      <c r="U14" s="50">
+        <f>AVERAGE(U4:U13)</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="50"/>
+      <c r="W14" s="50">
+        <f>AVERAGE(W4:W13)</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="50"/>
+      <c r="Y14" s="50">
+        <f>AVERAGE(Y4:Y13)</f>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="50"/>
+      <c r="AA14" s="50">
+        <f>AVERAGE(AA4:AA13)</f>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="50"/>
+      <c r="AC14" s="50">
+        <f>AVERAGE(AC4:AC13)</f>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="50"/>
+      <c r="AE14" s="50">
+        <f>AVERAGE(AE4:AE13)</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="50"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B15" s="52"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-    </row>
-    <row r="23" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="C23" s="2"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
     </row>
     <row r="24" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C24" s="2"/>
@@ -3173,39 +3210,42 @@
     <row r="38" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C38" s="2"/>
     </row>
+    <row r="39" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="C39" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="AE14:AF14"/>
+    <mergeCell ref="B4:B12"/>
+    <mergeCell ref="B15:D16"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="Y14:Z14"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AC14:AD14"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AC13:AD13"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AE13:AF13"/>
-    <mergeCell ref="B4:B11"/>
-    <mergeCell ref="B14:D15"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="Y13:Z13"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3229,7 +3269,7 @@
               <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>D4:D12</xm:sqref>
+          <xm:sqref>D4:D13</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
